--- a/AAAGameData/DataTables/CardTable.xlsx
+++ b/AAAGameData/DataTables/CardTable.xlsx
@@ -1,40 +1,714 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="105">
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>CardTable</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>IconId</t>
+  </si>
+  <si>
+    <t>PrefabConfig</t>
+  </si>
+  <si>
+    <t>SpiritCost</t>
+  </si>
+  <si>
+    <t>TargetType</t>
+  </si>
+  <si>
+    <t>CastRange</t>
+  </si>
+  <si>
+    <t>AreaRadius</t>
+  </si>
+  <si>
+    <t>DamageType</t>
+  </si>
+  <si>
+    <t>DamageCoeff</t>
+  </si>
+  <si>
+    <t>BaseDamage</t>
+  </si>
+  <si>
+    <t>InstantBuffs</t>
+  </si>
+  <si>
+    <t>HitBuffs</t>
+  </si>
+  <si>
+    <t>ParamsConfig</t>
+  </si>
+  <si>
+    <t>EffectId</t>
+  </si>
+  <si>
+    <t>HitEffectId</t>
+  </si>
+  <si>
+    <t>EffectSpawnHeight</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>UnlockCondition</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>卡牌ID</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>卡牌名称</t>
+  </si>
+  <si>
+    <t>卡牌描述</t>
+  </si>
+  <si>
+    <t>卡牌图标资源ID</t>
+  </si>
+  <si>
+    <t>预制体配置JSON</t>
+  </si>
+  <si>
+    <t>灵力消耗</t>
+  </si>
+  <si>
+    <t>目标类型(1=自身 2=友方单体 3=友方全体 4=敌方单体 5=敌方全体 6=全场)</t>
+  </si>
+  <si>
+    <t>施法范围(0=无限制)</t>
+  </si>
+  <si>
+    <t>AOE半径(0=单体)</t>
+  </si>
+  <si>
+    <t>伤害类型(0=无 1=物理 2=魔法 3=真实)</t>
+  </si>
+  <si>
+    <t>伤害系数</t>
+  </si>
+  <si>
+    <t>基础固定伤害</t>
+  </si>
+  <si>
+    <t>释放时施加的Buff列表</t>
+  </si>
+  <si>
+    <t>命中目标时施加的Buff列表</t>
+  </si>
+  <si>
+    <t>策略卡参数配置JSON</t>
+  </si>
+  <si>
+    <t>技能特效资源ID</t>
+  </si>
+  <si>
+    <t>受击特效资源ID</t>
+  </si>
+  <si>
+    <t>特效生成高度偏移</t>
+  </si>
+  <si>
+    <t>稀有度(1=普通 2=稀有 3=史诗 4=传说)</t>
+  </si>
+  <si>
+    <t>解锁条件</t>
+  </si>
+  <si>
+    <t>神圣庇护</t>
+  </si>
+  <si>
+    <t>为所有友方单位提供护盾，吸收伤害</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20101}</t>
+  </si>
+  <si>
+    <t>10301:3</t>
+  </si>
+  <si>
+    <t>{"shieldAmount":100,"duration":5}</t>
+  </si>
+  <si>
+    <t>烈焰风暴</t>
+  </si>
+  <si>
+    <t>对敌方全体造成魔法伤害</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20102}</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>10302:5</t>
+  </si>
+  <si>
+    <t>{"burnDuration":3}</t>
+  </si>
+  <si>
+    <t>时间回溯</t>
+  </si>
+  <si>
+    <t>使一个友方单位恢复到3秒前的状态</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20103}</t>
+  </si>
+  <si>
+    <t>{"rewindSeconds":3}</t>
+  </si>
+  <si>
+    <t>战争号角</t>
+  </si>
+  <si>
+    <t>提升全体友方攻击力和移动速度</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20104}</t>
+  </si>
+  <si>
+    <t>10303:3,10304:3</t>
+  </si>
+  <si>
+    <t>{"atkBonus":0.3,"spdBonus":0.2,"duration":8}</t>
+  </si>
+  <si>
+    <t>暗影突袭</t>
+  </si>
+  <si>
+    <t>对单个敌人造成高额物理伤害并眩晕</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20105,"projectilePrefab":20106}</t>
+  </si>
+  <si>
+    <t>10305:5</t>
+  </si>
+  <si>
+    <t>{"stunDuration":2}</t>
+  </si>
+  <si>
+    <t>生命汲取</t>
+  </si>
+  <si>
+    <t>对敌方全体造成伤害并为自身回复生命</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20107}</t>
+  </si>
+  <si>
+    <t>10306:5</t>
+  </si>
+  <si>
+    <t>{"healRatio":0.5}</t>
+  </si>
+  <si>
+    <t>冰霜新星</t>
+  </si>
+  <si>
+    <t>冰冻范围内所有敌人</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20108}</t>
+  </si>
+  <si>
+    <t>10307:5</t>
+  </si>
+  <si>
+    <t>{"freezeDuration":3}</t>
+  </si>
+  <si>
+    <t>狂暴</t>
+  </si>
+  <si>
+    <t>使自身进入狂暴状态，大幅提升攻击力但降低防御</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20109}</t>
+  </si>
+  <si>
+    <t>10308:1</t>
+  </si>
+  <si>
+    <t>{"atkBonus":0.8,"defPenalty":-0.3,"duration":10}</t>
+  </si>
+  <si>
+    <t>群体治疗</t>
+  </si>
+  <si>
+    <t>恢复所有友方单位的生命值</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20110}</t>
+  </si>
+  <si>
+    <t>10309:3</t>
+  </si>
+  <si>
+    <t>{"healAmount":150}</t>
+  </si>
+  <si>
+    <t>雷霆一击</t>
+  </si>
+  <si>
+    <t>召唤闪电对单个敌人造成真实伤害</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20111}</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>混乱诅咒</t>
+  </si>
+  <si>
+    <t>使敌方全体陷入混乱，有概率攻击队友</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20112}</t>
+  </si>
+  <si>
+    <t>10310:5</t>
+  </si>
+  <si>
+    <t>{"confuseDuration":4,"confuseChance":0.3}</t>
+  </si>
+  <si>
+    <t>不屈意志</t>
+  </si>
+  <si>
+    <t>复活一个阵亡的友方单位</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20113}</t>
+  </si>
+  <si>
+    <t>10311:5</t>
+  </si>
+  <si>
+    <t>{"reviveHpRatio":0.5}</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,88 +716,315 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -406,148 +1307,998 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:V16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="49" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="50" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="12" max="12" width="37" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="26" customWidth="1"/>
+    <col min="17" max="17" width="50" customWidth="1"/>
+    <col min="18" max="19" width="16" customWidth="1"/>
+    <col min="20" max="20" width="19" customWidth="1"/>
+    <col min="21" max="21" width="37" customWidth="1"/>
+    <col min="22" max="22" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>CardTable</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
+    <row r="1" spans="1:22">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>SpriteId</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Desc</t>
-        </is>
+    <row r="2" spans="1:22">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+    <row r="3" spans="1:22">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="n"/>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>卡牌名称</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>卡牌图标资源ID</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>卡牌描述</t>
-        </is>
+    <row r="4" ht="27" spans="1:22">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="1" t="n">
+    <row r="5" ht="15" customHeight="1" spans="1:22">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1201</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="1">
+        <v>30</v>
+      </c>
+      <c r="I5" s="1">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R5" s="1">
+        <v>30101</v>
+      </c>
+      <c r="S5" s="1">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="U5" s="1">
+        <v>2</v>
+      </c>
+      <c r="V5" s="1"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" spans="1:22">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1202</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="1">
+        <v>50</v>
+      </c>
+      <c r="I6" s="1">
+        <v>5</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>5</v>
+      </c>
+      <c r="L6" s="1">
+        <v>2</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>150</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="R6" s="1">
+        <v>30102</v>
+      </c>
+      <c r="S6" s="1">
+        <v>30201</v>
+      </c>
+      <c r="T6" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>群体圣光</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>1201</v>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>所有队友回复20点HP</t>
-        </is>
-      </c>
+      <c r="U6" s="1">
+        <v>3</v>
+      </c>
+      <c r="V6" s="1"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" spans="1:22">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1203</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="1">
+        <v>40</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2</v>
+      </c>
+      <c r="J7" s="1">
+        <v>10</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="1">
+        <v>30103</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="U7" s="1">
+        <v>3</v>
+      </c>
+      <c r="V7" s="1"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:22">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1204</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="1">
+        <v>35</v>
+      </c>
+      <c r="I8" s="1">
+        <v>3</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="R8" s="1">
+        <v>30104</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1">
+        <v>1</v>
+      </c>
+      <c r="U8" s="1">
+        <v>2</v>
+      </c>
+      <c r="V8" s="1"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:22">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1205</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="1">
+        <v>45</v>
+      </c>
+      <c r="I9" s="1">
+        <v>4</v>
+      </c>
+      <c r="J9" s="1">
+        <v>15</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="R9" s="1">
+        <v>30105</v>
+      </c>
+      <c r="S9" s="1">
+        <v>30202</v>
+      </c>
+      <c r="T9" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="U9" s="1">
+        <v>3</v>
+      </c>
+      <c r="V9" s="1"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="1:22">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1206</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" s="1">
+        <v>55</v>
+      </c>
+      <c r="I10" s="1">
+        <v>5</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>8</v>
+      </c>
+      <c r="L10" s="1">
+        <v>2</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>120</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="R10" s="1">
+        <v>30106</v>
+      </c>
+      <c r="S10" s="1">
+        <v>30203</v>
+      </c>
+      <c r="T10" s="1">
+        <v>1</v>
+      </c>
+      <c r="U10" s="1">
+        <v>3</v>
+      </c>
+      <c r="V10" s="1"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="1:22">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1">
+        <v>1007</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1207</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" s="1">
+        <v>40</v>
+      </c>
+      <c r="I11" s="1">
+        <v>5</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>6</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="R11" s="1">
+        <v>30107</v>
+      </c>
+      <c r="S11" s="1">
+        <v>30204</v>
+      </c>
+      <c r="T11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="U11" s="1">
+        <v>2</v>
+      </c>
+      <c r="V11" s="1"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="1:22">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1">
+        <v>1008</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1208</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="1">
+        <v>25</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="R12" s="1">
+        <v>30108</v>
+      </c>
+      <c r="S12" s="1">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="U12" s="1">
+        <v>2</v>
+      </c>
+      <c r="V12" s="1"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="1:22">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1">
+        <v>1009</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1209</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" s="1">
+        <v>45</v>
+      </c>
+      <c r="I13" s="1">
+        <v>3</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="R13" s="1">
+        <v>30109</v>
+      </c>
+      <c r="S13" s="1">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1">
+        <v>1</v>
+      </c>
+      <c r="U13" s="1">
+        <v>2</v>
+      </c>
+      <c r="V13" s="1"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:22">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1">
+        <v>1010</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1210</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H14" s="1">
+        <v>60</v>
+      </c>
+      <c r="I14" s="1">
+        <v>4</v>
+      </c>
+      <c r="J14" s="1">
+        <v>20</v>
+      </c>
+      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>3</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>200</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="R14" s="1">
+        <v>30110</v>
+      </c>
+      <c r="S14" s="1">
+        <v>30205</v>
+      </c>
+      <c r="T14" s="1">
+        <v>2</v>
+      </c>
+      <c r="U14" s="1">
+        <v>4</v>
+      </c>
+      <c r="V14" s="1"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:22">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1">
+        <v>1011</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1211</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H15" s="1">
+        <v>50</v>
+      </c>
+      <c r="I15" s="1">
+        <v>5</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="R15" s="1">
+        <v>30111</v>
+      </c>
+      <c r="S15" s="1">
+        <v>30206</v>
+      </c>
+      <c r="T15" s="1">
+        <v>1</v>
+      </c>
+      <c r="U15" s="1">
+        <v>3</v>
+      </c>
+      <c r="V15" s="1"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:22">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1">
+        <v>1012</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1212</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="1">
+        <v>80</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2</v>
+      </c>
+      <c r="J16" s="1">
+        <v>10</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R16" s="1">
+        <v>30112</v>
+      </c>
+      <c r="S16" s="1">
+        <v>0</v>
+      </c>
+      <c r="T16" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="U16" s="1">
+        <v>4</v>
+      </c>
+      <c r="V16" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/AAAGameData/DataTables/CardTable.xlsx
+++ b/AAAGameData/DataTables/CardTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="114">
   <si>
     <t>#</t>
   </si>
@@ -56,9 +56,6 @@
     <t>TargetType</t>
   </si>
   <si>
-    <t>CastRange</t>
-  </si>
-  <si>
     <t>AreaRadius</t>
   </si>
   <si>
@@ -129,9 +126,6 @@
   </si>
   <si>
     <t>目标类型(1=自身 2=友方单体 3=友方全体 4=敌方单体 5=敌方全体 6=全场)</t>
-  </si>
-  <si>
-    <t>施法范围(0=无限制)</t>
   </si>
   <si>
     <t>AOE半径(0=单体)</t>
@@ -1339,8 +1333,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:V16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -1351,22 +1345,21 @@
     <col min="7" max="7" width="49" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="50" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="37" customWidth="1"/>
-    <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="22" customWidth="1"/>
-    <col min="16" max="16" width="26" customWidth="1"/>
-    <col min="17" max="17" width="50" customWidth="1"/>
-    <col min="18" max="19" width="16" customWidth="1"/>
-    <col min="20" max="20" width="19" customWidth="1"/>
-    <col min="21" max="21" width="37" customWidth="1"/>
-    <col min="22" max="22" width="17" customWidth="1"/>
-    <col min="23" max="23" width="43.4444444444444" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="37" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="26" customWidth="1"/>
+    <col min="16" max="16" width="50" customWidth="1"/>
+    <col min="17" max="18" width="16" customWidth="1"/>
+    <col min="19" max="19" width="19" customWidth="1"/>
+    <col min="20" max="20" width="37" customWidth="1"/>
+    <col min="21" max="21" width="17" customWidth="1"/>
+    <col min="22" max="22" width="43.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1392,9 +1385,8 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1459,167 +1451,158 @@
       <c r="V2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="K3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="O3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="T3" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="U3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="V3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="W3" t="s">
-        <v>24</v>
+      <c r="V3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:23">
+    <row r="4" ht="27" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" t="s">
         <v>45</v>
       </c>
-      <c r="V4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="W4" t="s">
-        <v>47</v>
-      </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:23">
+    <row r="5" ht="15" customHeight="1" spans="1:22">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1001</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F5" s="1">
         <v>1201</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H5" s="1">
         <v>30</v>
@@ -1628,7 +1611,7 @@
         <v>3</v>
       </c>
       <c r="J5" s="1">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="K5" s="1">
         <v>0</v>
@@ -1639,50 +1622,47 @@
       <c r="M5" s="1">
         <v>0</v>
       </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1" t="s">
+      <c r="N5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>30101</v>
+      </c>
+      <c r="R5" s="1">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="T5" s="1">
+        <v>2</v>
+      </c>
+      <c r="U5" s="1"/>
+      <c r="V5" t="s">
         <v>51</v>
       </c>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R5" s="1">
-        <v>30101</v>
-      </c>
-      <c r="S5" s="1">
-        <v>0</v>
-      </c>
-      <c r="T5" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="U5" s="1">
-        <v>2</v>
-      </c>
-      <c r="V5" s="1"/>
-      <c r="W5" t="s">
-        <v>53</v>
-      </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:23">
+    <row r="6" ht="15" customHeight="1" spans="1:22">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1002</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F6" s="1">
         <v>1202</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H6" s="1">
         <v>50</v>
@@ -1691,63 +1671,60 @@
         <v>5</v>
       </c>
       <c r="J6" s="1">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="K6" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L6" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1">
         <v>150</v>
       </c>
+      <c r="N6" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="O6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="Q6" s="1">
+        <v>30102</v>
+      </c>
+      <c r="R6" s="1">
+        <v>30201</v>
+      </c>
+      <c r="S6" s="1">
+        <v>1</v>
+      </c>
+      <c r="T6" s="1">
+        <v>3</v>
+      </c>
+      <c r="U6" s="1"/>
+      <c r="V6" t="s">
         <v>58</v>
       </c>
-      <c r="Q6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="R6" s="1">
-        <v>30102</v>
-      </c>
-      <c r="S6" s="1">
-        <v>30201</v>
-      </c>
-      <c r="T6" s="1">
-        <v>1</v>
-      </c>
-      <c r="U6" s="1">
-        <v>3</v>
-      </c>
-      <c r="V6" s="1"/>
-      <c r="W6" t="s">
-        <v>60</v>
-      </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:23">
+    <row r="7" ht="15" customHeight="1" spans="1:22">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>1003</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F7" s="1">
         <v>1203</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H7" s="1">
         <v>40</v>
@@ -1756,7 +1733,7 @@
         <v>2</v>
       </c>
       <c r="J7" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K7" s="1">
         <v>0</v>
@@ -1767,50 +1744,47 @@
       <c r="M7" s="1">
         <v>0</v>
       </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1" t="s">
-        <v>64</v>
+      <c r="N7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>30103</v>
       </c>
       <c r="R7" s="1">
-        <v>30103</v>
+        <v>0</v>
       </c>
       <c r="S7" s="1">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T7" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="U7" s="1">
         <v>3</v>
       </c>
-      <c r="V7" s="1"/>
-      <c r="W7" t="s">
-        <v>65</v>
+      <c r="U7" s="1"/>
+      <c r="V7" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:23">
+    <row r="8" ht="15" customHeight="1" spans="1:22">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>1004</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F8" s="1">
         <v>1204</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H8" s="1">
         <v>35</v>
@@ -1819,7 +1793,7 @@
         <v>3</v>
       </c>
       <c r="J8" s="1">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="K8" s="1">
         <v>0</v>
@@ -1830,50 +1804,47 @@
       <c r="M8" s="1">
         <v>0</v>
       </c>
-      <c r="N8" s="1">
-        <v>0</v>
-      </c>
-      <c r="O8" s="1" t="s">
+      <c r="N8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>30104</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1">
+        <v>1</v>
+      </c>
+      <c r="T8" s="1">
+        <v>2</v>
+      </c>
+      <c r="U8" s="1"/>
+      <c r="V8" t="s">
         <v>69</v>
       </c>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R8" s="1">
-        <v>30104</v>
-      </c>
-      <c r="S8" s="1">
-        <v>0</v>
-      </c>
-      <c r="T8" s="1">
-        <v>1</v>
-      </c>
-      <c r="U8" s="1">
-        <v>2</v>
-      </c>
-      <c r="V8" s="1"/>
-      <c r="W8" t="s">
-        <v>71</v>
-      </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:23">
+    <row r="9" ht="15" customHeight="1" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>1005</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F9" s="1">
         <v>1205</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H9" s="1">
         <v>45</v>
@@ -1882,63 +1853,60 @@
         <v>4</v>
       </c>
       <c r="J9" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="1">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="M9" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="N9" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="P9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>30105</v>
+      </c>
+      <c r="R9" s="1">
+        <v>30202</v>
+      </c>
+      <c r="S9" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="T9" s="1">
+        <v>3</v>
+      </c>
+      <c r="U9" s="1"/>
+      <c r="V9" t="s">
         <v>75</v>
       </c>
-      <c r="Q9" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="R9" s="1">
-        <v>30105</v>
-      </c>
-      <c r="S9" s="1">
-        <v>30202</v>
-      </c>
-      <c r="T9" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="U9" s="1">
-        <v>3</v>
-      </c>
-      <c r="V9" s="1"/>
-      <c r="W9" t="s">
-        <v>77</v>
-      </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:23">
+    <row r="10" ht="15" customHeight="1" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>1006</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F10" s="1">
         <v>1206</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H10" s="1">
         <v>55</v>
@@ -1947,61 +1915,58 @@
         <v>5</v>
       </c>
       <c r="J10" s="1">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="K10" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L10" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" s="1">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1">
         <v>120</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1" t="s">
-        <v>81</v>
+      <c r="N10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>30106</v>
       </c>
       <c r="R10" s="1">
-        <v>30106</v>
+        <v>30203</v>
       </c>
       <c r="S10" s="1">
-        <v>30203</v>
+        <v>1</v>
       </c>
       <c r="T10" s="1">
-        <v>1</v>
-      </c>
-      <c r="U10" s="1">
         <v>3</v>
       </c>
-      <c r="V10" s="1"/>
-      <c r="W10" t="s">
-        <v>82</v>
+      <c r="U10" s="1"/>
+      <c r="V10" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:23">
+    <row r="11" ht="15" customHeight="1" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>1007</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F11" s="1">
         <v>1207</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H11" s="1">
         <v>40</v>
@@ -2010,10 +1975,10 @@
         <v>5</v>
       </c>
       <c r="J11" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K11" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L11" s="1">
         <v>0</v>
@@ -2021,52 +1986,49 @@
       <c r="M11" s="1">
         <v>0</v>
       </c>
-      <c r="N11" s="1">
-        <v>0</v>
+      <c r="N11" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="P11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>30107</v>
+      </c>
+      <c r="R11" s="1">
+        <v>30204</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="T11" s="1">
+        <v>2</v>
+      </c>
+      <c r="U11" s="1"/>
+      <c r="V11" t="s">
         <v>86</v>
       </c>
-      <c r="Q11" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="R11" s="1">
-        <v>30107</v>
-      </c>
-      <c r="S11" s="1">
-        <v>30204</v>
-      </c>
-      <c r="T11" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="U11" s="1">
-        <v>2</v>
-      </c>
-      <c r="V11" s="1"/>
-      <c r="W11" t="s">
-        <v>88</v>
-      </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:23">
+    <row r="12" ht="15" customHeight="1" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>1008</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F12" s="1">
         <v>1208</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H12" s="1">
         <v>25</v>
@@ -2075,7 +2037,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K12" s="1">
         <v>0</v>
@@ -2086,50 +2048,47 @@
       <c r="M12" s="1">
         <v>0</v>
       </c>
-      <c r="N12" s="1">
-        <v>0</v>
-      </c>
-      <c r="O12" s="1" t="s">
+      <c r="N12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>30108</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="T12" s="1">
+        <v>2</v>
+      </c>
+      <c r="U12" s="1"/>
+      <c r="V12" t="s">
         <v>92</v>
       </c>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="R12" s="1">
-        <v>30108</v>
-      </c>
-      <c r="S12" s="1">
-        <v>0</v>
-      </c>
-      <c r="T12" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="U12" s="1">
-        <v>2</v>
-      </c>
-      <c r="V12" s="1"/>
-      <c r="W12" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:23">
+    <row r="13" ht="15" customHeight="1" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>1009</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F13" s="1">
         <v>1209</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H13" s="1">
         <v>45</v>
@@ -2138,7 +2097,7 @@
         <v>3</v>
       </c>
       <c r="J13" s="1">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="K13" s="1">
         <v>0</v>
@@ -2149,48 +2108,45 @@
       <c r="M13" s="1">
         <v>0</v>
       </c>
-      <c r="N13" s="1">
-        <v>0</v>
-      </c>
+      <c r="N13" s="1"/>
       <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1" t="s">
-        <v>98</v>
+      <c r="P13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>30109</v>
       </c>
       <c r="R13" s="1">
-        <v>30109</v>
+        <v>0</v>
       </c>
       <c r="S13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" s="1">
-        <v>1</v>
-      </c>
-      <c r="U13" s="1">
         <v>2</v>
       </c>
-      <c r="V13" s="1"/>
-      <c r="W13" t="s">
-        <v>99</v>
+      <c r="U13" s="1"/>
+      <c r="V13" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:23">
+    <row r="14" ht="15" customHeight="1" spans="1:22">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>1010</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F14" s="1">
         <v>1210</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
         <v>60</v>
@@ -2199,61 +2155,58 @@
         <v>4</v>
       </c>
       <c r="J14" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K14" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L14" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1">
         <v>200</v>
       </c>
-      <c r="O14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1" t="s">
-        <v>103</v>
+      <c r="N14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>30110</v>
       </c>
       <c r="R14" s="1">
-        <v>30110</v>
+        <v>30205</v>
       </c>
       <c r="S14" s="1">
-        <v>30205</v>
+        <v>2</v>
       </c>
       <c r="T14" s="1">
-        <v>2</v>
-      </c>
-      <c r="U14" s="1">
         <v>4</v>
       </c>
-      <c r="V14" s="1"/>
-      <c r="W14" t="s">
-        <v>104</v>
+      <c r="U14" s="1"/>
+      <c r="V14" t="s">
+        <v>102</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:23">
+    <row r="15" ht="15" customHeight="1" spans="1:22">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>1011</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F15" s="1">
         <v>1211</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H15" s="1">
         <v>50</v>
@@ -2262,7 +2215,7 @@
         <v>5</v>
       </c>
       <c r="J15" s="1">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -2273,52 +2226,49 @@
       <c r="M15" s="1">
         <v>0</v>
       </c>
-      <c r="N15" s="1">
-        <v>0</v>
+      <c r="N15" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="P15" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>30111</v>
+      </c>
+      <c r="R15" s="1">
+        <v>30206</v>
+      </c>
+      <c r="S15" s="1">
+        <v>1</v>
+      </c>
+      <c r="T15" s="1">
+        <v>3</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" t="s">
         <v>108</v>
       </c>
-      <c r="Q15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="R15" s="1">
-        <v>30111</v>
-      </c>
-      <c r="S15" s="1">
-        <v>30206</v>
-      </c>
-      <c r="T15" s="1">
-        <v>1</v>
-      </c>
-      <c r="U15" s="1">
-        <v>3</v>
-      </c>
-      <c r="V15" s="1"/>
-      <c r="W15" t="s">
-        <v>110</v>
-      </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:23">
+    <row r="16" ht="15" customHeight="1" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>1012</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F16" s="1">
         <v>1212</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H16" s="1">
         <v>80</v>
@@ -2327,7 +2277,7 @@
         <v>2</v>
       </c>
       <c r="J16" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K16" s="1">
         <v>0</v>
@@ -2338,29 +2288,26 @@
       <c r="M16" s="1">
         <v>0</v>
       </c>
-      <c r="N16" s="1">
-        <v>0</v>
-      </c>
+      <c r="N16" s="1"/>
       <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1" t="s">
-        <v>114</v>
+      <c r="P16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>30112</v>
       </c>
       <c r="R16" s="1">
-        <v>30112</v>
+        <v>0</v>
       </c>
       <c r="S16" s="1">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T16" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="U16" s="1">
         <v>4</v>
       </c>
-      <c r="V16" s="1"/>
-      <c r="W16" t="s">
-        <v>115</v>
+      <c r="U16" s="1"/>
+      <c r="V16" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/CardTable.xlsx
+++ b/AAAGameData/DataTables/CardTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="101">
   <si>
     <t>#</t>
   </si>
@@ -125,7 +125,7 @@
     <t>灵力消耗</t>
   </si>
   <si>
-    <t>目标类型(1=自身 2=友方单体 3=友方全体 4=敌方单体 5=敌方全体 6=全场)</t>
+    <t>目标类型(1=自身，2=全体友方（不含召唤师），3=全体友方，4=敌方全体，5=单体友方，6=范围内友方，7=范围内敌方，8=单体敌方)</t>
   </si>
   <si>
     <t>AOE半径(0=单体)</t>
@@ -176,12 +176,6 @@
     <t>{"effectPrefab":20101}</t>
   </si>
   <si>
-    <t>5001:5</t>
-  </si>
-  <si>
-    <t>{"shieldAmount":100,"duration":5}</t>
-  </si>
-  <si>
     <t>众神之光笼罩战场，守护者的誓言永不磨灭</t>
   </si>
   <si>
@@ -194,12 +188,6 @@
     <t>{"effectPrefab":20102}</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>5002:3</t>
-  </si>
-  <si>
     <t>{"burnDuration":3}</t>
   </si>
   <si>
@@ -230,12 +218,6 @@
     <t>{"effectPrefab":20104}</t>
   </si>
   <si>
-    <t>5003:8</t>
-  </si>
-  <si>
-    <t>{"atkBonus":0.3,"spdBonus":0.2,"duration":8}</t>
-  </si>
-  <si>
     <t>英雄们听到了召唤，战士的血液在沸腾</t>
   </si>
   <si>
@@ -248,9 +230,6 @@
     <t>{"effectPrefab":20105,"projectilePrefab":20106}</t>
   </si>
   <si>
-    <t>5005:2</t>
-  </si>
-  <si>
     <t>{"stunDuration":2}</t>
   </si>
   <si>
@@ -281,9 +260,6 @@
     <t>{"effectPrefab":20108}</t>
   </si>
   <si>
-    <t>5007:3</t>
-  </si>
-  <si>
     <t>{"freezeDuration":3}</t>
   </si>
   <si>
@@ -299,12 +275,6 @@
     <t>{"effectPrefab":20109}</t>
   </si>
   <si>
-    <t>5008:10</t>
-  </si>
-  <si>
-    <t>{"atkBonus":0.8,"defPenalty":-0.3,"duration":10}</t>
-  </si>
-  <si>
     <t>力量爆发，野兽苏醒，舍生忘死的战士之歌</t>
   </si>
   <si>
@@ -332,9 +302,6 @@
     <t>{"effectPrefab":20111}</t>
   </si>
   <si>
-    <t>{}</t>
-  </si>
-  <si>
     <t>诸神之怒，天雷无可抵挡</t>
   </si>
   <si>
@@ -345,12 +312,6 @@
   </si>
   <si>
     <t>{"effectPrefab":20112}</t>
-  </si>
-  <si>
-    <t>5010:4</t>
-  </si>
-  <si>
-    <t>{"confuseDuration":4,"confuseChance":0.3}</t>
   </si>
   <si>
     <t>诅咒扭曲心智，自相残杀的悲剧</t>
@@ -1344,7 +1305,7 @@
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="49" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="50" customWidth="1"/>
+    <col min="9" max="9" width="52.75" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
     <col min="11" max="11" width="37" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
@@ -1518,7 +1479,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" ht="27" spans="1:22">
+    <row r="4" ht="40.5" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1622,13 +1583,11 @@
       <c r="M5" s="1">
         <v>0</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>49</v>
+      <c r="N5" s="1">
+        <v>5001</v>
       </c>
       <c r="O5" s="1"/>
-      <c r="P5" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="P5" s="1"/>
       <c r="Q5" s="1">
         <v>30101</v>
       </c>
@@ -1643,7 +1602,7 @@
       </c>
       <c r="U5" s="1"/>
       <c r="V5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:22">
@@ -1653,22 +1612,22 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F6" s="1">
         <v>1202</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H6" s="1">
         <v>50</v>
       </c>
       <c r="I6" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" s="1">
         <v>99</v>
@@ -1682,14 +1641,12 @@
       <c r="M6" s="1">
         <v>150</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>56</v>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1">
+        <v>5002</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Q6" s="1">
         <v>30102</v>
@@ -1705,7 +1662,7 @@
       </c>
       <c r="U6" s="1"/>
       <c r="V6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:22">
@@ -1715,22 +1672,22 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F7" s="1">
         <v>1203</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H7" s="1">
         <v>40</v>
       </c>
       <c r="I7" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J7" s="1">
         <v>5</v>
@@ -1744,12 +1701,10 @@
       <c r="M7" s="1">
         <v>0</v>
       </c>
-      <c r="N7" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="Q7" s="1">
         <v>30103</v>
@@ -1765,7 +1720,7 @@
       </c>
       <c r="U7" s="1"/>
       <c r="V7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:22">
@@ -1775,16 +1730,16 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F8" s="1">
         <v>1204</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H8" s="1">
         <v>35</v>
@@ -1804,13 +1759,11 @@
       <c r="M8" s="1">
         <v>0</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>67</v>
+      <c r="N8" s="1">
+        <v>5003</v>
       </c>
       <c r="O8" s="1"/>
-      <c r="P8" s="1" t="s">
-        <v>68</v>
-      </c>
+      <c r="P8" s="1"/>
       <c r="Q8" s="1">
         <v>30104</v>
       </c>
@@ -1825,7 +1778,7 @@
       </c>
       <c r="U8" s="1"/>
       <c r="V8" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:22">
@@ -1835,22 +1788,22 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F9" s="1">
         <v>1205</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H9" s="1">
         <v>45</v>
       </c>
       <c r="I9" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J9" s="1">
         <v>5</v>
@@ -1864,14 +1817,12 @@
       <c r="M9" s="1">
         <v>0</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>73</v>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1">
+        <v>5005</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="Q9" s="1">
         <v>30105</v>
@@ -1887,7 +1838,7 @@
       </c>
       <c r="U9" s="1"/>
       <c r="V9" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:22">
@@ -1897,22 +1848,22 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F10" s="1">
         <v>1206</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H10" s="1">
         <v>55</v>
       </c>
       <c r="I10" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10" s="1">
         <v>99</v>
@@ -1926,12 +1877,10 @@
       <c r="M10" s="1">
         <v>120</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="Q10" s="1">
         <v>30106</v>
@@ -1947,7 +1896,7 @@
       </c>
       <c r="U10" s="1"/>
       <c r="V10" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:22">
@@ -1957,22 +1906,22 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F11" s="1">
         <v>1207</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H11" s="1">
         <v>40</v>
       </c>
       <c r="I11" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J11" s="1">
         <v>8</v>
@@ -1986,14 +1935,12 @@
       <c r="M11" s="1">
         <v>0</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>84</v>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1">
+        <v>5007</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="Q11" s="1">
         <v>30107</v>
@@ -2009,7 +1956,7 @@
       </c>
       <c r="U11" s="1"/>
       <c r="V11" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:22">
@@ -2019,16 +1966,16 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F12" s="1">
         <v>1208</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H12" s="1">
         <v>25</v>
@@ -2048,13 +1995,11 @@
       <c r="M12" s="1">
         <v>0</v>
       </c>
-      <c r="N12" s="1" t="s">
-        <v>90</v>
+      <c r="N12" s="1">
+        <v>5008</v>
       </c>
       <c r="O12" s="1"/>
-      <c r="P12" s="1" t="s">
-        <v>91</v>
-      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1">
         <v>30108</v>
       </c>
@@ -2069,7 +2014,7 @@
       </c>
       <c r="U12" s="1"/>
       <c r="V12" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:22">
@@ -2079,16 +2024,16 @@
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F13" s="1">
         <v>1209</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="H13" s="1">
         <v>45</v>
@@ -2111,7 +2056,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="Q13" s="1">
         <v>30109</v>
@@ -2127,7 +2072,7 @@
       </c>
       <c r="U13" s="1"/>
       <c r="V13" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:22">
@@ -2137,22 +2082,22 @@
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F14" s="1">
         <v>1210</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="H14" s="1">
         <v>60</v>
       </c>
       <c r="I14" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J14" s="1">
         <v>5</v>
@@ -2166,13 +2111,9 @@
       <c r="M14" s="1">
         <v>200</v>
       </c>
-      <c r="N14" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="N14" s="1"/>
       <c r="O14" s="1"/>
-      <c r="P14" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="P14" s="1"/>
       <c r="Q14" s="1">
         <v>30110</v>
       </c>
@@ -2187,7 +2128,7 @@
       </c>
       <c r="U14" s="1"/>
       <c r="V14" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:22">
@@ -2197,22 +2138,22 @@
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="F15" s="1">
         <v>1211</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="H15" s="1">
         <v>50</v>
       </c>
       <c r="I15" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15" s="1">
         <v>99</v>
@@ -2226,15 +2167,11 @@
       <c r="M15" s="1">
         <v>0</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>107</v>
-      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1">
+        <v>5009</v>
+      </c>
+      <c r="P15" s="1"/>
       <c r="Q15" s="1">
         <v>30111</v>
       </c>
@@ -2249,7 +2186,7 @@
       </c>
       <c r="U15" s="1"/>
       <c r="V15" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:22">
@@ -2259,22 +2196,22 @@
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="F16" s="1">
         <v>1212</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="H16" s="1">
         <v>80</v>
       </c>
       <c r="I16" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J16" s="1">
         <v>5</v>
@@ -2291,7 +2228,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="Q16" s="1">
         <v>30112</v>
@@ -2307,7 +2244,7 @@
       </c>
       <c r="U16" s="1"/>
       <c r="V16" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/CardTable.xlsx
+++ b/AAAGameData/DataTables/CardTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="193">
   <si>
     <t>#</t>
   </si>
@@ -176,6 +176,9 @@
     <t>{"effectPrefab":20101}</t>
   </si>
   <si>
+    <t>5001</t>
+  </si>
+  <si>
     <t>众神之光笼罩战场，守护者的誓言永不磨灭</t>
   </si>
   <si>
@@ -188,6 +191,9 @@
     <t>{"effectPrefab":20102}</t>
   </si>
   <si>
+    <t>5002</t>
+  </si>
+  <si>
     <t>{"burnDuration":3}</t>
   </si>
   <si>
@@ -218,6 +224,9 @@
     <t>{"effectPrefab":20104}</t>
   </si>
   <si>
+    <t>5003</t>
+  </si>
+  <si>
     <t>英雄们听到了召唤，战士的血液在沸腾</t>
   </si>
   <si>
@@ -230,6 +239,9 @@
     <t>{"effectPrefab":20105,"projectilePrefab":20106}</t>
   </si>
   <si>
+    <t>5005</t>
+  </si>
+  <si>
     <t>{"stunDuration":2}</t>
   </si>
   <si>
@@ -260,6 +272,9 @@
     <t>{"effectPrefab":20108}</t>
   </si>
   <si>
+    <t>5007</t>
+  </si>
+  <si>
     <t>{"freezeDuration":3}</t>
   </si>
   <si>
@@ -275,6 +290,9 @@
     <t>{"effectPrefab":20109}</t>
   </si>
   <si>
+    <t>5008</t>
+  </si>
+  <si>
     <t>力量爆发，野兽苏醒，舍生忘死的战士之歌</t>
   </si>
   <si>
@@ -314,6 +332,9 @@
     <t>{"effectPrefab":20112}</t>
   </si>
   <si>
+    <t>5009</t>
+  </si>
+  <si>
     <t>诅咒扭曲心智，自相残杀的悲剧</t>
   </si>
   <si>
@@ -330,6 +351,261 @@
   </si>
   <si>
     <t>死而复生，英雄的传奇永不落幕</t>
+  </si>
+  <si>
+    <t>反伤之盾</t>
+  </si>
+  <si>
+    <t>为自身获得反伤效果，返回受到伤害的30%</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20114}</t>
+  </si>
+  <si>
+    <t>5011</t>
+  </si>
+  <si>
+    <t>护盾闪耀，敌人的攻击将成为自己的灭亡</t>
+  </si>
+  <si>
+    <t>圣域防线</t>
+  </si>
+  <si>
+    <t>为范围内友方增加护甲，提升防御</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20115}</t>
+  </si>
+  <si>
+    <t>5012</t>
+  </si>
+  <si>
+    <t>圣光铸就防线，守护者的堡垒无坚不摧</t>
+  </si>
+  <si>
+    <t>护盾再生</t>
+  </si>
+  <si>
+    <t>友方护盾每3秒恢复50点（持续15秒）</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20116}</t>
+  </si>
+  <si>
+    <t>5013</t>
+  </si>
+  <si>
+    <t>护盾在阳光下缓缓恢复，防御永不削弱</t>
+  </si>
+  <si>
+    <t>救赎之光</t>
+  </si>
+  <si>
+    <t>恢复单个友方单位150点生命值并驱散负面效果</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20117}</t>
+  </si>
+  <si>
+    <t>{"healAmount":150,"dispelDebuffs":true}</t>
+  </si>
+  <si>
+    <t>圣光笼罩，所有诅咒烟消云散，重获新生</t>
+  </si>
+  <si>
+    <t>血源强化</t>
+  </si>
+  <si>
+    <t>临时增加全体友方最大生命值+30%，持续15秒</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20118}</t>
+  </si>
+  <si>
+    <t>5014</t>
+  </si>
+  <si>
+    <t>古老血脉觉醒，生命力在苏醒</t>
+  </si>
+  <si>
+    <t>吸血之刃</t>
+  </si>
+  <si>
+    <t>对单体敌方造成高额物理伤害并吸血</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20119,"projectilePrefab":20120}</t>
+  </si>
+  <si>
+    <t>5015</t>
+  </si>
+  <si>
+    <t>{"lifestealRatio":0.4}</t>
+  </si>
+  <si>
+    <t>刀刃吸食生命，血液在指尖流淌</t>
+  </si>
+  <si>
+    <t>灾厄之雷</t>
+  </si>
+  <si>
+    <t>对敌方全体造成魔法伤害并施加灼烧</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20121}</t>
+  </si>
+  <si>
+    <t>5016</t>
+  </si>
+  <si>
+    <t>{"burnLayers":2}</t>
+  </si>
+  <si>
+    <t>天地失色，灾厄之雷吞没一切生命</t>
+  </si>
+  <si>
+    <t>护甲破碎</t>
+  </si>
+  <si>
+    <t>对单体敌方造成伤害并破坏护甲</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20122}</t>
+  </si>
+  <si>
+    <t>5017</t>
+  </si>
+  <si>
+    <t>{"armorReduction":5,"duration":15}</t>
+  </si>
+  <si>
+    <t>护甲在一击间粉碎，防御化为泡影</t>
+  </si>
+  <si>
+    <t>虚弱诅咒</t>
+  </si>
+  <si>
+    <t>敌方全体陷入虚弱，降低攻击力30%，持续15秒</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20123}</t>
+  </si>
+  <si>
+    <t>5018</t>
+  </si>
+  <si>
+    <t>{"attackReduction":0.3,"duration":15}</t>
+  </si>
+  <si>
+    <t>诅咒之力落下，战士失去了曾经的威力</t>
+  </si>
+  <si>
+    <t>沉默之符</t>
+  </si>
+  <si>
+    <t>单体敌人陷入沉默，禁用技能10秒</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20124}</t>
+  </si>
+  <si>
+    <t>5019</t>
+  </si>
+  <si>
+    <t>{"silenceDuration":10}</t>
+  </si>
+  <si>
+    <t>神秘符号浮现，敌人失去了发动技能的能力</t>
+  </si>
+  <si>
+    <t>嘲讽之声</t>
+  </si>
+  <si>
+    <t>敌方全体陷入嘲讽10秒，强制攻击你</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20125}</t>
+  </si>
+  <si>
+    <t>5020</t>
+  </si>
+  <si>
+    <t>{"tauntDuration":10}</t>
+  </si>
+  <si>
+    <t>挑衅之声传出，敌人无法转身离开</t>
+  </si>
+  <si>
+    <t>减速诅咒</t>
+  </si>
+  <si>
+    <t>敌方移动速度降低50%，持续15秒</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20126}</t>
+  </si>
+  <si>
+    <t>5021</t>
+  </si>
+  <si>
+    <t>{"speedReduction":0.5,"duration":15}</t>
+  </si>
+  <si>
+    <t>缓慢的诅咒铺开，敌人步履蹒跚</t>
+  </si>
+  <si>
+    <t>剧毒之雾</t>
+  </si>
+  <si>
+    <t>敌方全体中毒，持续15秒，每秒掉血5点</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20127}</t>
+  </si>
+  <si>
+    <t>5022</t>
+  </si>
+  <si>
+    <t>{"poisonDamagePerSecond":5,"duration":15}</t>
+  </si>
+  <si>
+    <t>暗绿色的毒雾弥漫战场，生命在腐蚀中消逝</t>
+  </si>
+  <si>
+    <t>伤害转移</t>
+  </si>
+  <si>
+    <t>转移友方单位的伤害到另一个友方（50%转移率，20秒）</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20128}</t>
+  </si>
+  <si>
+    <t>5023</t>
+  </si>
+  <si>
+    <t>{"transferDuration":20,"transferPercentage":0.5}</t>
+  </si>
+  <si>
+    <t>力量纽带相连，伤害在盟友间分散</t>
+  </si>
+  <si>
+    <t>绝对零度</t>
+  </si>
+  <si>
+    <t>完全冻结敌方全体25秒（无法行动、无法释放技能）</t>
+  </si>
+  <si>
+    <t>{"effectPrefab":20129}</t>
+  </si>
+  <si>
+    <t>5024</t>
+  </si>
+  <si>
+    <t>{"freezeDuration":25}</t>
+  </si>
+  <si>
+    <t>永恒的绝对零度降临，时间在此彻底冻结</t>
   </si>
 </sst>
 </file>
@@ -342,7 +618,14 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -798,148 +1081,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1294,30 +1577,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="5" max="5" width="50" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="49" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="52.75" customWidth="1"/>
+    <col min="9" max="9" width="50" customWidth="1"/>
     <col min="10" max="10" width="17" customWidth="1"/>
     <col min="11" max="11" width="37" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
     <col min="14" max="14" width="22" customWidth="1"/>
     <col min="15" max="15" width="26" customWidth="1"/>
-    <col min="16" max="16" width="50" customWidth="1"/>
-    <col min="17" max="18" width="16" customWidth="1"/>
+    <col min="16" max="16" width="43" customWidth="1"/>
+    <col min="17" max="17" width="50" customWidth="1"/>
+    <col min="18" max="18" width="16" customWidth="1"/>
     <col min="19" max="19" width="19" customWidth="1"/>
     <col min="20" max="20" width="37" customWidth="1"/>
     <col min="21" max="21" width="17" customWidth="1"/>
-    <col min="22" max="22" width="43.4416666666667" customWidth="1"/>
+    <col min="22" max="22" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -1346,6 +1630,7 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
@@ -1475,7 +1760,7 @@
       <c r="U3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V3" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1543,7 +1828,7 @@
       <c r="U4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="V4" t="s">
+      <c r="V4" s="1" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1583,8 +1868,8 @@
       <c r="M5" s="1">
         <v>0</v>
       </c>
-      <c r="N5" s="1">
-        <v>5001</v>
+      <c r="N5" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
@@ -1601,8 +1886,8 @@
         <v>2</v>
       </c>
       <c r="U5" s="1"/>
-      <c r="V5" t="s">
-        <v>49</v>
+      <c r="V5" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:22">
@@ -1612,16 +1897,16 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F6" s="1">
         <v>1202</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H6" s="1">
         <v>50</v>
@@ -1642,11 +1927,11 @@
         <v>150</v>
       </c>
       <c r="N6" s="1"/>
-      <c r="O6" s="1">
-        <v>5002</v>
+      <c r="O6" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Q6" s="1">
         <v>30102</v>
@@ -1661,8 +1946,8 @@
         <v>3</v>
       </c>
       <c r="U6" s="1"/>
-      <c r="V6" t="s">
-        <v>54</v>
+      <c r="V6" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:22">
@@ -1672,16 +1957,16 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F7" s="1">
         <v>1203</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H7" s="1">
         <v>40</v>
@@ -1704,7 +1989,7 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q7" s="1">
         <v>30103</v>
@@ -1719,8 +2004,8 @@
         <v>3</v>
       </c>
       <c r="U7" s="1"/>
-      <c r="V7" t="s">
-        <v>59</v>
+      <c r="V7" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:22">
@@ -1730,16 +2015,16 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F8" s="1">
         <v>1204</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H8" s="1">
         <v>35</v>
@@ -1759,8 +2044,8 @@
       <c r="M8" s="1">
         <v>0</v>
       </c>
-      <c r="N8" s="1">
-        <v>5003</v>
+      <c r="N8" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
@@ -1777,8 +2062,8 @@
         <v>2</v>
       </c>
       <c r="U8" s="1"/>
-      <c r="V8" t="s">
-        <v>63</v>
+      <c r="V8" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:22">
@@ -1788,16 +2073,16 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F9" s="1">
         <v>1205</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H9" s="1">
         <v>45</v>
@@ -1818,11 +2103,11 @@
         <v>0</v>
       </c>
       <c r="N9" s="1"/>
-      <c r="O9" s="1">
-        <v>5005</v>
+      <c r="O9" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="Q9" s="1">
         <v>30105</v>
@@ -1837,8 +2122,8 @@
         <v>3</v>
       </c>
       <c r="U9" s="1"/>
-      <c r="V9" t="s">
-        <v>68</v>
+      <c r="V9" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:22">
@@ -1848,16 +2133,16 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F10" s="1">
         <v>1206</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H10" s="1">
         <v>55</v>
@@ -1880,7 +2165,7 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="Q10" s="1">
         <v>30106</v>
@@ -1895,8 +2180,8 @@
         <v>3</v>
       </c>
       <c r="U10" s="1"/>
-      <c r="V10" t="s">
-        <v>73</v>
+      <c r="V10" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:22">
@@ -1906,16 +2191,16 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F11" s="1">
         <v>1207</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H11" s="1">
         <v>40</v>
@@ -1936,11 +2221,11 @@
         <v>0</v>
       </c>
       <c r="N11" s="1"/>
-      <c r="O11" s="1">
-        <v>5007</v>
+      <c r="O11" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="Q11" s="1">
         <v>30107</v>
@@ -1955,8 +2240,8 @@
         <v>2</v>
       </c>
       <c r="U11" s="1"/>
-      <c r="V11" t="s">
-        <v>78</v>
+      <c r="V11" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:22">
@@ -1966,16 +2251,16 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F12" s="1">
         <v>1208</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H12" s="1">
         <v>25</v>
@@ -1995,8 +2280,8 @@
       <c r="M12" s="1">
         <v>0</v>
       </c>
-      <c r="N12" s="1">
-        <v>5008</v>
+      <c r="N12" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
@@ -2013,8 +2298,8 @@
         <v>2</v>
       </c>
       <c r="U12" s="1"/>
-      <c r="V12" t="s">
-        <v>82</v>
+      <c r="V12" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:22">
@@ -2024,16 +2309,16 @@
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F13" s="1">
         <v>1209</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H13" s="1">
         <v>45</v>
@@ -2056,7 +2341,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="Q13" s="1">
         <v>30109</v>
@@ -2071,8 +2356,8 @@
         <v>2</v>
       </c>
       <c r="U13" s="1"/>
-      <c r="V13" t="s">
-        <v>87</v>
+      <c r="V13" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:22">
@@ -2082,16 +2367,16 @@
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F14" s="1">
         <v>1210</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H14" s="1">
         <v>60</v>
@@ -2127,8 +2412,8 @@
         <v>4</v>
       </c>
       <c r="U14" s="1"/>
-      <c r="V14" t="s">
-        <v>91</v>
+      <c r="V14" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:22">
@@ -2138,16 +2423,16 @@
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F15" s="1">
         <v>1211</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
         <v>50</v>
@@ -2168,8 +2453,8 @@
         <v>0</v>
       </c>
       <c r="N15" s="1"/>
-      <c r="O15" s="1">
-        <v>5009</v>
+      <c r="O15" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="P15" s="1"/>
       <c r="Q15" s="1">
@@ -2185,8 +2470,8 @@
         <v>3</v>
       </c>
       <c r="U15" s="1"/>
-      <c r="V15" t="s">
-        <v>95</v>
+      <c r="V15" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:22">
@@ -2196,16 +2481,16 @@
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F16" s="1">
         <v>1212</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H16" s="1">
         <v>80</v>
@@ -2228,7 +2513,7 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="Q16" s="1">
         <v>30112</v>
@@ -2243,8 +2528,898 @@
         <v>4</v>
       </c>
       <c r="U16" s="1"/>
-      <c r="V16" t="s">
-        <v>100</v>
+      <c r="V16" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:22">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1">
+        <v>1013</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1213</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" s="1">
+        <v>25</v>
+      </c>
+      <c r="I17" s="1">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1">
+        <v>5</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1">
+        <v>30113</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+      <c r="S17" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="T17" s="1">
+        <v>2</v>
+      </c>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:22">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1">
+        <v>1014</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1214</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" s="1">
+        <v>35</v>
+      </c>
+      <c r="I18" s="1">
+        <v>6</v>
+      </c>
+      <c r="J18" s="1">
+        <v>8</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1">
+        <v>30114</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
+        <v>1</v>
+      </c>
+      <c r="T18" s="1">
+        <v>3</v>
+      </c>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:22">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1">
+        <v>1015</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1215</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" s="1">
+        <v>40</v>
+      </c>
+      <c r="I19" s="1">
+        <v>5</v>
+      </c>
+      <c r="J19" s="1">
+        <v>5</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1">
+        <v>30115</v>
+      </c>
+      <c r="R19" s="1">
+        <v>0</v>
+      </c>
+      <c r="S19" s="1">
+        <v>1</v>
+      </c>
+      <c r="T19" s="1">
+        <v>3</v>
+      </c>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:22">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1">
+        <v>1016</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1216</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H20" s="1">
+        <v>35</v>
+      </c>
+      <c r="I20" s="1">
+        <v>5</v>
+      </c>
+      <c r="J20" s="1">
+        <v>5</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>30116</v>
+      </c>
+      <c r="R20" s="1">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="T20" s="1">
+        <v>3</v>
+      </c>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:22">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1">
+        <v>1017</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1217</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H21" s="1">
+        <v>45</v>
+      </c>
+      <c r="I21" s="1">
+        <v>3</v>
+      </c>
+      <c r="J21" s="1">
+        <v>99</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1">
+        <v>30117</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>1</v>
+      </c>
+      <c r="T21" s="1">
+        <v>3</v>
+      </c>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="1:22">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1">
+        <v>1018</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1218</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H22" s="1">
+        <v>50</v>
+      </c>
+      <c r="I22" s="1">
+        <v>8</v>
+      </c>
+      <c r="J22" s="1">
+        <v>5</v>
+      </c>
+      <c r="K22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
+        <v>2</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>30118</v>
+      </c>
+      <c r="R22" s="1">
+        <v>30301</v>
+      </c>
+      <c r="S22" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="T22" s="1">
+        <v>3</v>
+      </c>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:22">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1">
+        <v>1019</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1219</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H23" s="1">
+        <v>55</v>
+      </c>
+      <c r="I23" s="1">
+        <v>4</v>
+      </c>
+      <c r="J23" s="1">
+        <v>99</v>
+      </c>
+      <c r="K23" s="1">
+        <v>2</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>80</v>
+      </c>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>30119</v>
+      </c>
+      <c r="R23" s="1">
+        <v>30302</v>
+      </c>
+      <c r="S23" s="1">
+        <v>2</v>
+      </c>
+      <c r="T23" s="1">
+        <v>3</v>
+      </c>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" spans="1:22">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1">
+        <v>1020</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1220</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H24" s="1">
+        <v>45</v>
+      </c>
+      <c r="I24" s="1">
+        <v>8</v>
+      </c>
+      <c r="J24" s="1">
+        <v>5</v>
+      </c>
+      <c r="K24" s="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
+        <v>50</v>
+      </c>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>30120</v>
+      </c>
+      <c r="R24" s="1">
+        <v>30303</v>
+      </c>
+      <c r="S24" s="1">
+        <v>1</v>
+      </c>
+      <c r="T24" s="1">
+        <v>3</v>
+      </c>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" spans="1:22">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1">
+        <v>1021</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1221</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25" s="1">
+        <v>40</v>
+      </c>
+      <c r="I25" s="1">
+        <v>4</v>
+      </c>
+      <c r="J25" s="1">
+        <v>99</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>30121</v>
+      </c>
+      <c r="R25" s="1">
+        <v>30304</v>
+      </c>
+      <c r="S25" s="1">
+        <v>1</v>
+      </c>
+      <c r="T25" s="1">
+        <v>2</v>
+      </c>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="1:22">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1">
+        <v>1022</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1222</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H26" s="1">
+        <v>35</v>
+      </c>
+      <c r="I26" s="1">
+        <v>8</v>
+      </c>
+      <c r="J26" s="1">
+        <v>5</v>
+      </c>
+      <c r="K26" s="1">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>30122</v>
+      </c>
+      <c r="R26" s="1">
+        <v>30305</v>
+      </c>
+      <c r="S26" s="1">
+        <v>1</v>
+      </c>
+      <c r="T26" s="1">
+        <v>3</v>
+      </c>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" spans="1:22">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1">
+        <v>1023</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1223</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H27" s="1">
+        <v>25</v>
+      </c>
+      <c r="I27" s="1">
+        <v>4</v>
+      </c>
+      <c r="J27" s="1">
+        <v>99</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1">
+        <v>0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>30123</v>
+      </c>
+      <c r="R27" s="1">
+        <v>30306</v>
+      </c>
+      <c r="S27" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="T27" s="1">
+        <v>2</v>
+      </c>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:22">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1">
+        <v>1024</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1224</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H28" s="1">
+        <v>35</v>
+      </c>
+      <c r="I28" s="1">
+        <v>4</v>
+      </c>
+      <c r="J28" s="1">
+        <v>99</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>30124</v>
+      </c>
+      <c r="R28" s="1">
+        <v>30307</v>
+      </c>
+      <c r="S28" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="T28" s="1">
+        <v>2</v>
+      </c>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" spans="1:22">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1">
+        <v>1025</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1225</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H29" s="1">
+        <v>30</v>
+      </c>
+      <c r="I29" s="1">
+        <v>4</v>
+      </c>
+      <c r="J29" s="1">
+        <v>99</v>
+      </c>
+      <c r="K29" s="1">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>30125</v>
+      </c>
+      <c r="R29" s="1">
+        <v>30308</v>
+      </c>
+      <c r="S29" s="1">
+        <v>1</v>
+      </c>
+      <c r="T29" s="1">
+        <v>2</v>
+      </c>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" spans="1:22">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1">
+        <v>1026</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1226</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H30" s="1">
+        <v>30</v>
+      </c>
+      <c r="I30" s="1">
+        <v>5</v>
+      </c>
+      <c r="J30" s="1">
+        <v>5</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>30126</v>
+      </c>
+      <c r="R30" s="1">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>1</v>
+      </c>
+      <c r="T30" s="1">
+        <v>3</v>
+      </c>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" spans="1:22">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1">
+        <v>1027</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1227</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="H31" s="1">
+        <v>50</v>
+      </c>
+      <c r="I31" s="1">
+        <v>4</v>
+      </c>
+      <c r="J31" s="1">
+        <v>99</v>
+      </c>
+      <c r="K31" s="1">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>30127</v>
+      </c>
+      <c r="R31" s="1">
+        <v>30309</v>
+      </c>
+      <c r="S31" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="T31" s="1">
+        <v>4</v>
+      </c>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/CardTable.xlsx
+++ b/AAAGameData/DataTables/CardTable.xlsx
@@ -2530,7 +2530,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L16" s="1">
         <v>0</v>

--- a/AAAGameData/DataTables/CardTable.xlsx
+++ b/AAAGameData/DataTables/CardTable.xlsx
@@ -2530,7 +2530,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="L16" s="1">
         <v>0</v>

--- a/AAAGameData/DataTables/CardTable.xlsx
+++ b/AAAGameData/DataTables/CardTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -603,14 +603,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1066,148 +1059,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1563,7 +1556,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W30"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -1574,7 +1567,7 @@
     <col min="7" max="7" width="49" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="50" customWidth="1"/>
-    <col min="10" max="10" width="15.625" customWidth="1"/>
+    <col min="10" max="10" width="15.6296296296296" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="37" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
@@ -1618,7 +1611,7 @@
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" ht="28.8" spans="1:23">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1756,7 +1749,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" ht="40.5" spans="1:23">
+    <row r="4" ht="43.2" spans="1:23">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>

--- a/AAAGameData/DataTables/CardTable.xlsx
+++ b/AAAGameData/DataTables/CardTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="181">
   <si>
     <t>#</t>
   </si>
@@ -557,34 +557,13 @@
     <t>暗绿色的毒雾弥漫战场，生命在腐蚀中消逝</t>
   </si>
   <si>
-    <t>伤害转移</t>
-  </si>
-  <si>
-    <t>转移友方单位的伤害到另一个友方（50%转移率，20秒）</t>
+    <t>绝对零度</t>
+  </si>
+  <si>
+    <t>完全冻结敌方全体10秒（无法行动、无法释放技能）</t>
   </si>
   <si>
     <t>{"effectPrefab":20127}</t>
-  </si>
-  <si>
-    <t>5022</t>
-  </si>
-  <si>
-    <t>{"transferDuration":20,"transferPercentage":0.5}</t>
-  </si>
-  <si>
-    <t>力量纽带相连，伤害在盟友间分散</t>
-  </si>
-  <si>
-    <t>绝对零度</t>
-  </si>
-  <si>
-    <t>完全冻结敌方全体10秒（无法行动、无法释放技能）</t>
-  </si>
-  <si>
-    <t>{"effectPrefab":20128}</t>
-  </si>
-  <si>
-    <t>5023</t>
   </si>
   <si>
     <t>{"freezeDuration":10}</t>
@@ -1555,7 +1534,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W30"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3321,16 +3300,16 @@
         <v>178</v>
       </c>
       <c r="H29" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I29" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J29" s="1">
         <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="L29" s="1">
         <v>0</v>
@@ -3341,91 +3320,28 @@
       <c r="N29" s="1">
         <v>0</v>
       </c>
-      <c r="O29" s="1" t="s">
+      <c r="O29" s="1"/>
+      <c r="P29" s="1">
+        <v>5022</v>
+      </c>
+      <c r="Q29" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="R29" s="1">
-        <v>30125</v>
+        <v>30126</v>
       </c>
       <c r="S29" s="1">
-        <v>0</v>
+        <v>30308</v>
       </c>
       <c r="T29" s="1">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="U29" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V29" s="1"/>
       <c r="W29" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" spans="1:23">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1">
-        <v>1026</v>
-      </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F30" s="1">
-        <v>1226</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H30" s="1">
-        <v>50</v>
-      </c>
-      <c r="I30" s="1">
-        <v>4</v>
-      </c>
-      <c r="J30" s="1">
-        <v>0</v>
-      </c>
-      <c r="K30" s="1">
-        <v>99</v>
-      </c>
-      <c r="L30" s="1">
-        <v>0</v>
-      </c>
-      <c r="M30" s="1">
-        <v>0</v>
-      </c>
-      <c r="N30" s="1">
-        <v>0</v>
-      </c>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="R30" s="1">
-        <v>30126</v>
-      </c>
-      <c r="S30" s="1">
-        <v>30308</v>
-      </c>
-      <c r="T30" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="U30" s="1">
-        <v>4</v>
-      </c>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/CardTable.xlsx
+++ b/AAAGameData/DataTables/CardTable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -269,7 +269,7 @@
     <t>黑暗力量苏醒，生命在掌心流转</t>
   </si>
   <si>
-    <t>冰霜新星</t>
+    <t>冰霜冲击</t>
   </si>
   <si>
     <t>冰冻范围内所有敌人</t>
@@ -1535,7 +1535,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:W29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -1546,7 +1546,7 @@
     <col min="7" max="7" width="49" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="50" customWidth="1"/>
-    <col min="10" max="10" width="15.6296296296296" customWidth="1"/>
+    <col min="10" max="10" width="15.6333333333333" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="37" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
@@ -1590,7 +1590,7 @@
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
     </row>
-    <row r="2" ht="28.8" spans="1:23">
+    <row r="2" spans="1:23">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" ht="43.2" spans="1:23">
+    <row r="4" ht="40.5" spans="1:23">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
